--- a/artfynd/A 53082-2025 artfynd.xlsx
+++ b/artfynd/A 53082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102132171</v>
+        <v>119064301</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>820064.2093364109</v>
+        <v>820364</v>
       </c>
       <c r="R2" t="n">
-        <v>7376925.029811565</v>
+        <v>7376791</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102132169</v>
+        <v>102153078</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>820154.0797639694</v>
+        <v>819979</v>
       </c>
       <c r="R3" t="n">
-        <v>7377190.042964674</v>
+        <v>7377028</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102132156</v>
+        <v>119064279</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>820058.4847883739</v>
+        <v>820359</v>
       </c>
       <c r="R4" t="n">
-        <v>7376921.941576344</v>
+        <v>7376786</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102132170</v>
+        <v>119064280</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>820064.3056050171</v>
+        <v>820411</v>
       </c>
       <c r="R5" t="n">
-        <v>7376934.758318735</v>
+        <v>7376781</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102132172</v>
+        <v>102153155</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>820058.4847883739</v>
+        <v>819997</v>
       </c>
       <c r="R6" t="n">
-        <v>7376921.941576344</v>
+        <v>7377011</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,92 +1131,78 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102153092</v>
+        <v>119064302</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>820027.0698663866</v>
+        <v>820510</v>
       </c>
       <c r="R7" t="n">
-        <v>7376962.459058869</v>
+        <v>7376913</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1226,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102153100</v>
+        <v>16889753</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1269,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>6500 m NO Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>820013.5420968633</v>
+        <v>820022</v>
       </c>
       <c r="R8" t="n">
-        <v>7376988.434393781</v>
+        <v>7377169</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1327,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering, inventerare Leif Nybom</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102153168</v>
+        <v>65425599</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1375,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>820030.6146487738</v>
+        <v>820240</v>
       </c>
       <c r="R9" t="n">
-        <v>7376977.442907666</v>
+        <v>7376877</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1429,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1454,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102153167</v>
+        <v>119064310</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1477,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>820032.5315415862</v>
+        <v>820563</v>
       </c>
       <c r="R10" t="n">
-        <v>7376999.527221329</v>
+        <v>7376834</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,6 +1545,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1683,15 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102153084</v>
+        <v>119064311</v>
       </c>
       <c r="B11" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,37 +1575,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>819994.6904634549</v>
+        <v>820411</v>
       </c>
       <c r="R11" t="n">
-        <v>7376976.142894406</v>
+        <v>7376794</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1629,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,6 +1643,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,15 +1662,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102153169</v>
+        <v>119064312</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,37 +1673,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>820020.0256074936</v>
+        <v>820509</v>
       </c>
       <c r="R12" t="n">
-        <v>7376967.31678207</v>
+        <v>7376830</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1727,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,12 +1762,7 @@
         <v>102153074</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1794,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>820026.3056507625</v>
+        <v>820026</v>
       </c>
       <c r="R13" t="n">
-        <v>7377011.361998586</v>
+        <v>7377011</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1980,19 +1827,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,19 +1856,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102153164</v>
+        <v>102132169</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2055,14 +1887,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>820019.5147435757</v>
+        <v>820154</v>
       </c>
       <c r="R14" t="n">
-        <v>7376996.40962743</v>
+        <v>7377190</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2092,19 +1924,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,62 +1941,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102153091</v>
+        <v>102132170</v>
       </c>
       <c r="B15" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>820014.4801025717</v>
+        <v>820064</v>
       </c>
       <c r="R15" t="n">
-        <v>7376987.327693305</v>
+        <v>7376935</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2204,19 +2021,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,31 +2038,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102153166</v>
+        <v>102132171</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2279,14 +2081,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>820021.2433413608</v>
+        <v>820064</v>
       </c>
       <c r="R16" t="n">
-        <v>7377009.5647527</v>
+        <v>7376925</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2316,19 +2118,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,62 +2135,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102153118</v>
+        <v>102132172</v>
       </c>
       <c r="B17" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blötmyrtjärnen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>819998.7045468562</v>
+        <v>820058</v>
       </c>
       <c r="R17" t="n">
-        <v>7376972.960860599</v>
+        <v>7376922</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,77 +2215,61 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102132210</v>
+        <v>102132173</v>
       </c>
       <c r="B18" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2508,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>820089.5482877879</v>
+        <v>820112</v>
       </c>
       <c r="R18" t="n">
-        <v>7377159.131534952</v>
+        <v>7376845</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2541,19 +2312,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,50 +2341,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102132209</v>
+        <v>102153157</v>
       </c>
       <c r="B19" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>820154.0797639694</v>
+        <v>819998</v>
       </c>
       <c r="R19" t="n">
-        <v>7377190.042964674</v>
+        <v>7377063</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2653,19 +2409,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,62 +2426,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102132211</v>
+        <v>102153158</v>
       </c>
       <c r="B20" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blötmyrtjärn..., Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>820058.4847883739</v>
+        <v>819988</v>
       </c>
       <c r="R20" t="n">
-        <v>7376921.941576344</v>
+        <v>7377031</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2765,19 +2506,9 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,62 +2523,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maj Aspebo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102153116</v>
+        <v>102153159</v>
       </c>
       <c r="B21" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>819970.4820137919</v>
+        <v>819990</v>
       </c>
       <c r="R21" t="n">
-        <v>7376992.79154869</v>
+        <v>7377002</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2877,28 +2603,17 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2917,50 +2632,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102153119</v>
+        <v>102153160</v>
       </c>
       <c r="B22" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>820007.9189857855</v>
+        <v>819994</v>
       </c>
       <c r="R22" t="n">
-        <v>7376970.377275091</v>
+        <v>7376989</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2990,28 +2700,17 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3030,50 +2729,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102153211</v>
+        <v>102153162</v>
       </c>
       <c r="B23" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>820020.1868365046</v>
+        <v>820001</v>
       </c>
       <c r="R23" t="n">
-        <v>7376948.305635695</v>
+        <v>7377018</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3103,28 +2797,17 @@
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-07</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3143,53 +2826,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119064285</v>
+        <v>102153163</v>
       </c>
       <c r="B24" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>820407</v>
+        <v>820007</v>
       </c>
       <c r="R24" t="n">
-        <v>7376839</v>
+        <v>7376975</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3213,12 +2891,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,19 +2923,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119064305</v>
+        <v>102153164</v>
       </c>
       <c r="B25" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3281,17 +2954,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>820413</v>
+        <v>820019</v>
       </c>
       <c r="R25" t="n">
-        <v>7376738</v>
+        <v>7376996</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3315,12 +2988,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,19 +3020,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119064309</v>
+        <v>102153166</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3383,17 +3051,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>820545</v>
+        <v>820021</v>
       </c>
       <c r="R26" t="n">
-        <v>7376845</v>
+        <v>7377009</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3417,12 +3085,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3449,53 +3117,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119064282</v>
+        <v>102153167</v>
       </c>
       <c r="B27" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>820559</v>
+        <v>820032</v>
       </c>
       <c r="R27" t="n">
-        <v>7376852</v>
+        <v>7376999</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3519,12 +3182,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,53 +3214,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119064319</v>
+        <v>102153168</v>
       </c>
       <c r="B28" t="n">
-        <v>57742</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102999</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>820406</v>
+        <v>820031</v>
       </c>
       <c r="R28" t="n">
-        <v>7376820</v>
+        <v>7376977</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3621,17 +3279,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Unge</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3658,53 +3311,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119064302</v>
+        <v>102153169</v>
       </c>
       <c r="B29" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>820510</v>
+        <v>820020</v>
       </c>
       <c r="R29" t="n">
-        <v>7376913</v>
+        <v>7376967</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3728,12 +3376,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,16 +3411,11 @@
         <v>119064304</v>
       </c>
       <c r="B30" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3862,35 +3505,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119064299</v>
+        <v>119064305</v>
       </c>
       <c r="B31" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3898,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>820574</v>
+        <v>820413</v>
       </c>
       <c r="R31" t="n">
-        <v>7376817</v>
+        <v>7376738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,37 +3602,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119064280</v>
+        <v>119064306</v>
       </c>
       <c r="B32" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4000,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>820411</v>
+        <v>820417</v>
       </c>
       <c r="R32" t="n">
-        <v>7376781</v>
+        <v>7376786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4062,37 +3699,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119064311</v>
+        <v>119064307</v>
       </c>
       <c r="B33" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4102,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>820411</v>
+        <v>820510</v>
       </c>
       <c r="R33" t="n">
-        <v>7376794</v>
+        <v>7376864</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4146,7 +3778,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4165,35 +3796,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119064296</v>
+        <v>119064308</v>
       </c>
       <c r="B34" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4201,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>820405</v>
+        <v>820516</v>
       </c>
       <c r="R34" t="n">
-        <v>7376801</v>
+        <v>7376844</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4263,37 +3893,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119064281</v>
+        <v>119064309</v>
       </c>
       <c r="B35" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4303,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>820394</v>
+        <v>820545</v>
       </c>
       <c r="R35" t="n">
-        <v>7376777</v>
+        <v>7376845</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,32 +3990,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119064315</v>
+        <v>119064313</v>
       </c>
       <c r="B36" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4398,17 +4018,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norra Blötmyrvägen, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>820406</v>
+        <v>820377</v>
       </c>
       <c r="R36" t="n">
-        <v>7376839</v>
+        <v>7376796</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,12 +4067,18 @@
           <t>2024-06-20</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4467,15 +4097,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119064290</v>
+        <v>119064294</v>
       </c>
       <c r="B37" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,21 +4108,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4507,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>820532</v>
+        <v>820406</v>
       </c>
       <c r="R37" t="n">
-        <v>7376844</v>
+        <v>7376839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,53 +4194,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119064288</v>
+        <v>102153091</v>
       </c>
       <c r="B38" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>820411</v>
+        <v>820014</v>
       </c>
       <c r="R38" t="n">
-        <v>7376736</v>
+        <v>7376987</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4639,12 +4259,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4671,57 +4291,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119064313</v>
+        <v>102153092</v>
       </c>
       <c r="B39" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>820377</v>
+        <v>820027</v>
       </c>
       <c r="R39" t="n">
-        <v>7376796</v>
+        <v>7376962</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4745,17 +4356,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,7 +4370,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4783,37 +4388,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119064294</v>
+        <v>119064284</v>
       </c>
       <c r="B40" t="n">
-        <v>79605</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4823,10 +4423,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>820406</v>
+        <v>820425</v>
       </c>
       <c r="R40" t="n">
-        <v>7376839</v>
+        <v>7376791</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4867,6 +4467,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4885,37 +4486,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119064307</v>
+        <v>119064285</v>
       </c>
       <c r="B41" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4925,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>820510</v>
+        <v>820407</v>
       </c>
       <c r="R41" t="n">
-        <v>7376864</v>
+        <v>7376839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,15 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119064287</v>
+        <v>119064314</v>
       </c>
       <c r="B42" t="n">
-        <v>97910</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,21 +4594,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>820421</v>
+        <v>820409</v>
       </c>
       <c r="R42" t="n">
-        <v>7376789</v>
+        <v>7376835</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5071,8 +4662,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5089,37 +4696,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119064312</v>
+        <v>119064315</v>
       </c>
       <c r="B43" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5129,10 +4731,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>820509</v>
+        <v>820406</v>
       </c>
       <c r="R43" t="n">
-        <v>7376830</v>
+        <v>7376839</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5191,15 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119064297</v>
+        <v>102132156</v>
       </c>
       <c r="B44" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,33 +4804,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>223597</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>820384</v>
+        <v>820058</v>
       </c>
       <c r="R44" t="n">
-        <v>7376776</v>
+        <v>7376922</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5257,12 +4858,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5277,27 +4878,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119064314</v>
+        <v>102153100</v>
       </c>
       <c r="B45" t="n">
-        <v>79640</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,37 +4901,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>820409</v>
+        <v>820014</v>
       </c>
       <c r="R45" t="n">
-        <v>7376835</v>
+        <v>7376988</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5359,12 +4955,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,24 +4969,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5407,37 +4987,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119064310</v>
+        <v>119064288</v>
       </c>
       <c r="B46" t="n">
-        <v>82303</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5447,10 +5022,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>820563</v>
+        <v>820411</v>
       </c>
       <c r="R46" t="n">
-        <v>7376834</v>
+        <v>7376736</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5066,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5510,15 +5084,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119064284</v>
+        <v>119064289</v>
       </c>
       <c r="B47" t="n">
-        <v>79634</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5526,21 +5095,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5550,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>820425</v>
+        <v>820515</v>
       </c>
       <c r="R47" t="n">
-        <v>7376791</v>
+        <v>7376839</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5594,7 +5163,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5613,37 +5181,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119064308</v>
+        <v>119064290</v>
       </c>
       <c r="B48" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5653,7 +5216,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>820516</v>
+        <v>820532</v>
       </c>
       <c r="R48" t="n">
         <v>7376844</v>
@@ -5715,53 +5278,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119064289</v>
+        <v>102153081</v>
       </c>
       <c r="B49" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>820515</v>
+        <v>820010</v>
       </c>
       <c r="R49" t="n">
-        <v>7376839</v>
+        <v>7376988</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5785,12 +5343,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5817,15 +5375,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119064279</v>
+        <v>119064319</v>
       </c>
       <c r="B50" t="n">
-        <v>90544</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5833,21 +5386,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>102999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5857,10 +5410,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>820359</v>
+        <v>820406</v>
       </c>
       <c r="R50" t="n">
-        <v>7376786</v>
+        <v>7376820</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5893,6 +5446,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Unge</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5919,15 +5477,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119064306</v>
+        <v>102153084</v>
       </c>
       <c r="B51" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5935,37 +5488,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>820417</v>
+        <v>819995</v>
       </c>
       <c r="R51" t="n">
-        <v>7376786</v>
+        <v>7376976</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5989,12 +5542,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6021,35 +5574,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119064298</v>
+        <v>119064282</v>
       </c>
       <c r="B52" t="n">
-        <v>97809</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223597</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6057,10 +5609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>820406</v>
+        <v>820559</v>
       </c>
       <c r="R52" t="n">
-        <v>7376773</v>
+        <v>7376852</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6119,53 +5671,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119064301</v>
+        <v>102132209</v>
       </c>
       <c r="B53" t="n">
-        <v>90540</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>820364</v>
+        <v>820154</v>
       </c>
       <c r="R53" t="n">
-        <v>7376791</v>
+        <v>7377190</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6189,12 +5736,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6209,27 +5756,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119064286</v>
+        <v>102132210</v>
       </c>
       <c r="B54" t="n">
-        <v>97910</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6237,37 +5779,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norra Blötmyrvägen, Nb</t>
+          <t>Blötmyrtjärn..., Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>820414</v>
+        <v>820089</v>
       </c>
       <c r="R54" t="n">
-        <v>7376784</v>
+        <v>7377159</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6291,12 +5833,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6311,15 +5853,1070 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>102132211</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Blötmyrtjärn..., Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>820058</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7376922</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>102153116</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Blötmyrtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>819970</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7376993</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>102153118</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Blötmyrtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>819999</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7376973</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>102153119</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Blötmyrtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>820008</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7376970</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>102153211</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Blötmyrtjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>820020</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7376948</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>119064286</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>820414</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7376784</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>119064287</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>820421</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7376789</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>119064296</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>820405</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7376801</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119064297</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>820384</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7376776</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>119064298</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>820406</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7376773</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>119064299</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Norra Blötmyrvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>820574</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7376817</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53082-2025 artfynd.xlsx
+++ b/artfynd/A 53082-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064312</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132173</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1450,6 +1490,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064304</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1547,6 +1592,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1644,6 +1694,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064306</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064309</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064313</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064284</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064285</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2350,6 +2435,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064314</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2447,6 +2537,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064315</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2544,6 +2639,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064288</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2641,6 +2741,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064289</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2738,6 +2843,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064290</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064319</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2937,6 +3052,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064282</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3034,6 +3154,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064286</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3131,6 +3256,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064287</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3224,6 +3354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064296</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3317,6 +3452,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064297</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3410,6 +3550,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064298</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3503,6 +3648,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064299</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3600,6 +3750,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153078</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3698,6 +3853,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153155</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3795,6 +3955,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064302</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3901,6 +4066,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16889753</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4003,6 +4173,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65425599</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4100,6 +4275,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153074</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4197,6 +4377,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132169</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4294,6 +4479,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132170</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4391,6 +4581,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132171</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4488,6 +4683,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132172</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4585,6 +4785,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153157</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4682,6 +4887,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153158</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4779,6 +4989,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153159</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4876,6 +5091,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153160</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4973,6 +5193,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153162</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5070,6 +5295,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153163</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5167,6 +5397,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153164</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5264,6 +5499,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153166</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5361,6 +5601,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153167</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5458,6 +5703,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153168</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5555,6 +5805,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153169</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5652,6 +5907,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119064307</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5749,6 +6009,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153091</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5846,6 +6111,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153092</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5943,6 +6213,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132156</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6040,6 +6315,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153100</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6137,6 +6417,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153081</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6234,6 +6519,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153084</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6331,6 +6621,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132209</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6428,6 +6723,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132210</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6525,6 +6825,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102132211</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6623,6 +6928,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153116</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6721,6 +7031,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153118</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6819,6 +7134,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153119</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6917,8 +7237,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102153211</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>